--- a/isolated_excel/Table 2 - Current Update.xlsx
+++ b/isolated_excel/Table 2 - Current Update.xlsx
@@ -442,7 +442,7 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.295628487903424</v>
+        <v>1.307936068641449</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448012329545969</v>
+        <v>3.42868537831944</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.194520884974981</v>
+        <v>1.207602368089744</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.65217391304348</v>
+        <v>95.68965517241379</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>69.56521739130434</v>
+        <v>69.82758620689656</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.310344827586207</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30.43478260869566</v>
+        <v>30.17241379310345</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909092</v>
+        <v>3.696486486486487</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.616317163875842</v>
+        <v>3.605292357575083</v>
       </c>
     </row>
     <row r="7">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.295628487903424</v>
+        <v>1.307936068641449</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.983943837120484</v>
+        <v>3.972276416934467</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.510533237481414</v>
+        <v>4.492835307894532</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182456</v>
+        <v>2.651927277101982</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4323133842228444</v>
+        <v>-0.4416507937681062</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.54330321288962</v>
+        <v>8.629009524988723</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5443369456982423</v>
+        <v>0.5738724008555964</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349508</v>
+        <v>0.8810417533861374</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2872450816096581</v>
+        <v>0.2911159610821309</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287689</v>
+        <v>14.56591488300176</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4658018365243973</v>
+        <v>0.4722666723968901</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612905</v>
+        <v>94.54147465437789</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.061929277735463</v>
+        <v>2.081338762374768</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -734,7 +734,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 2 - Current Update.xlsx
+++ b/isolated_excel/Table 2 - Current Update.xlsx
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.307936068641449</v>
+        <v>1.293802428707488</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.42868537831944</v>
+        <v>3.408469136214709</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.207602368089744</v>
+        <v>1.194224232291563</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.68965517241379</v>
+        <v>95.72649572649573</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>69.82758620689656</v>
+        <v>69.23076923076923</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.310344827586207</v>
+        <v>4.273504273504273</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>30.17241379310345</v>
+        <v>30.76923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.696486486486487</v>
+        <v>3.673214285714287</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3.605292357575083</v>
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-4.008802771462106</v>
+        <v>-3.907049911244601</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.307936068641449</v>
+        <v>1.293802428707488</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.972276416934467</v>
+        <v>3.961386811469624</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.492835307894532</v>
+        <v>4.476039261568972</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.651927277101982</v>
+        <v>2.664304280248351</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4416507937681062</v>
+        <v>-0.4335291363518803</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.629009524988723</v>
+        <v>8.710085873783012</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5738724008555964</v>
+        <v>0.5905376312934969</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8810417533861374</v>
+        <v>0.8782644727023218</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2911159610821309</v>
+        <v>0.2890507328244424</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.56591488300176</v>
+        <v>14.54247474070697</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4722666723968901</v>
+        <v>0.4691411362145471</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.54147465437789</v>
+        <v>94.79262672811062</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.081338762374768</v>
+        <v>2.076223234619459</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -734,7 +734,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
